--- a/data/processed/data_processed_missing_20250709.xlsx
+++ b/data/processed/data_processed_missing_20250709.xlsx
@@ -404,7 +404,7 @@
         <v>24.52</v>
       </c>
       <c r="F2">
-        <v>0.0199320625</v>
+        <v>0.019932063</v>
       </c>
     </row>
     <row r="3">
@@ -506,7 +506,7 @@
         <v>0.15</v>
       </c>
       <c r="F7">
-        <v>0.00174966666666667</v>
+        <v>0.001749667</v>
       </c>
     </row>
     <row r="8">
@@ -548,7 +548,7 @@
         <v>0.91</v>
       </c>
       <c r="F9">
-        <v>0.00249722233333333</v>
+        <v>0.002497222</v>
       </c>
     </row>
     <row r="10">
@@ -608,7 +608,7 @@
         <v>0.555</v>
       </c>
       <c r="F12">
-        <v>0.00155546666666667</v>
+        <v>0.001555467</v>
       </c>
     </row>
     <row r="13">
@@ -644,7 +644,7 @@
         <v>0.91</v>
       </c>
       <c r="F14">
-        <v>0.0023097855</v>
+        <v>0.002309786</v>
       </c>
     </row>
     <row r="15">
@@ -662,17 +662,17 @@
         </is>
       </c>
       <c r="F15">
-        <v>0.00089225</v>
+        <v>0.000892</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Desmodium canadense</t>
+          <t>Desmodium illinoense</t>
         </is>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -680,31 +680,34 @@
         </is>
       </c>
       <c r="F16">
-        <v>0.0051</v>
+        <v>0.0066</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Desmodium illinoense</t>
+          <t>Desmodium paniculatum</t>
         </is>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
+      <c r="E17">
+        <v>0.91</v>
+      </c>
       <c r="F17">
-        <v>0.0066</v>
+        <v>0.00273</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Desmodium paniculatum</t>
+          <t>Digitaria cognata</t>
         </is>
       </c>
       <c r="B18">
@@ -712,63 +715,63 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fabaceae</t>
-        </is>
-      </c>
-      <c r="E18">
-        <v>0.91</v>
+          <t>Poaceae</t>
+        </is>
       </c>
       <c r="F18">
-        <v>0.00273</v>
+        <v>0.00055</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Digitaria cognata</t>
+          <t>Drymocallis arguta</t>
         </is>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poaceae</t>
-        </is>
+          <t>Rosaceae</t>
+        </is>
+      </c>
+      <c r="E19">
+        <v>0.91</v>
       </c>
       <c r="F19">
-        <v>0.00055</v>
+        <v>0.000142</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Drymocallis arguta</t>
+          <t>Echinacea pallida</t>
         </is>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rosaceae</t>
+          <t>Asteraceae</t>
         </is>
       </c>
       <c r="E20">
-        <v>0.91</v>
+        <v>0.37</v>
       </c>
       <c r="F20">
-        <v>0.00014158325</v>
+        <v>0.0049695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Echinacea pallida</t>
+          <t>Echinacea purpurea</t>
         </is>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -779,34 +782,34 @@
         <v>0.37</v>
       </c>
       <c r="F21">
-        <v>0.0049695</v>
+        <v>0.002164</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Echinacea purpurea</t>
+          <t>Elaeagnus umbellata</t>
         </is>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Asteraceae</t>
+          <t>Elaeagnaceae</t>
         </is>
       </c>
       <c r="E22">
-        <v>0.37</v>
+        <v>4.6</v>
       </c>
       <c r="F22">
-        <v>0.002164</v>
+        <v>0.0152625</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Elaeagnus umbellata</t>
+          <t>Elymus canadensis</t>
         </is>
       </c>
       <c r="B23">
@@ -814,20 +817,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Elaeagnaceae</t>
+          <t>Poaceae</t>
         </is>
       </c>
       <c r="E23">
-        <v>4.6</v>
+        <v>0.91</v>
       </c>
       <c r="F23">
-        <v>0.0152625</v>
+        <v>0.0042035</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Elymus canadensis</t>
+          <t>Elymus virginicus</t>
         </is>
       </c>
       <c r="B24">
@@ -839,16 +842,16 @@
         </is>
       </c>
       <c r="E24">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="F24">
-        <v>0.0042035</v>
+        <v>0.004918556</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Elymus virginicus</t>
+          <t>Eragrostis cilianensis</t>
         </is>
       </c>
       <c r="B25">
@@ -860,16 +863,16 @@
         </is>
       </c>
       <c r="E25">
-        <v>0.76</v>
+        <v>0.303333333</v>
       </c>
       <c r="F25">
-        <v>0.00491855566666667</v>
+        <v>7.13E-05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Eragrostis cilianensis</t>
+          <t>Eragrostis spectabilis</t>
         </is>
       </c>
       <c r="B26">
@@ -881,16 +884,16 @@
         </is>
       </c>
       <c r="E26">
-        <v>0.303333333333333</v>
+        <v>0.27</v>
       </c>
       <c r="F26">
-        <v>7.13333333333333E-05</v>
+        <v>0.000257</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Eragrostis spectabilis</t>
+          <t>Erechtites hieraciifolius</t>
         </is>
       </c>
       <c r="B27">
@@ -898,56 +901,53 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poaceae</t>
-        </is>
-      </c>
-      <c r="E27">
-        <v>0.27</v>
+          <t>Asteraceae</t>
+        </is>
       </c>
       <c r="F27">
-        <v>0.0002574</v>
+        <v>0.00056</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Erechtites hieraciifolius</t>
+          <t>Eryngium yuccifolium</t>
         </is>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Asteraceae</t>
+          <t>Apiaceae</t>
         </is>
       </c>
       <c r="F28">
-        <v>0.000560111</v>
+        <v>0.00382</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Eryngium yuccifolium</t>
+          <t>Euphorbia maculata</t>
         </is>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Apiaceae</t>
+          <t>Euphorbiaceae</t>
         </is>
       </c>
       <c r="F29">
-        <v>0.00382</v>
+        <v>0.000177</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Euphorbia maculata</t>
+          <t>Euthamia graminifolia</t>
         </is>
       </c>
       <c r="B30">
@@ -955,17 +955,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Euphorbiaceae</t>
-        </is>
+          <t>Asteraceae</t>
+        </is>
+      </c>
+      <c r="E30">
+        <v>0.6</v>
       </c>
       <c r="F30">
-        <v>0.000176833333333333</v>
+        <v>0.000106</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Euthamia graminifolia</t>
+          <t>Fagopyrum esculentum</t>
         </is>
       </c>
       <c r="B31">
@@ -973,20 +976,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Asteraceae</t>
+          <t>Polygonaceae</t>
         </is>
       </c>
       <c r="E31">
-        <v>0.6</v>
+        <v>0.828333333</v>
       </c>
       <c r="F31">
-        <v>0.000106</v>
+        <v>0.025273</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Fagopyrum esculentum</t>
+          <t>Gamochaeta purpurea</t>
         </is>
       </c>
       <c r="B32">
@@ -994,20 +997,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Polygonaceae</t>
+          <t>Asteraceae</t>
         </is>
       </c>
       <c r="E32">
-        <v>0.828333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="F32">
-        <v>0.025273</v>
+        <v>3.83E-05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gamochaeta purpurea</t>
+          <t>Geum canadense</t>
         </is>
       </c>
       <c r="B33">
@@ -1015,20 +1018,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Asteraceae</t>
+          <t>Rosaceae</t>
         </is>
       </c>
       <c r="E33">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="F33">
-        <v>3.825E-05</v>
+        <v>0.00515</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Geum canadense</t>
+          <t>Gleditsia triacanthos</t>
         </is>
       </c>
       <c r="B34">
@@ -1036,20 +1039,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rosaceae</t>
+          <t>Fabaceae</t>
         </is>
       </c>
       <c r="E34">
-        <v>1.2</v>
+        <v>27.16</v>
       </c>
       <c r="F34">
-        <v>0.00515</v>
+        <v>0.176454889</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Gleditsia triacanthos</t>
+          <t>Hackelia virginiana</t>
         </is>
       </c>
       <c r="B35">
@@ -1057,32 +1060,29 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fabaceae</t>
-        </is>
-      </c>
-      <c r="E35">
-        <v>27.16</v>
+          <t>Boraginaceae</t>
+        </is>
       </c>
       <c r="F35">
-        <v>0.1764548886</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Hackelia virginiana</t>
+          <t>Helianthus occidentalis</t>
         </is>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boraginaceae</t>
+          <t>Asteraceae</t>
         </is>
       </c>
       <c r="F36">
-        <v>0.0026</v>
+        <v>0.00221</v>
       </c>
     </row>
     <row r="37">
@@ -1103,7 +1103,7 @@
         <v>0.32</v>
       </c>
       <c r="F37">
-        <v>0.000814182</v>
+        <v>0.0008140000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1223,7 +1223,7 @@
         <v>167.43</v>
       </c>
       <c r="F43">
-        <v>0.0215308335</v>
+        <v>0.021530834</v>
       </c>
     </row>
     <row r="44">
@@ -1244,7 +1244,7 @@
         <v>1.5</v>
       </c>
       <c r="F44">
-        <v>0.00223369466666667</v>
+        <v>0.002233695</v>
       </c>
     </row>
     <row r="45">
@@ -1265,7 +1265,7 @@
         <v>0.2</v>
       </c>
       <c r="F45">
-        <v>9.0125E-05</v>
+        <v>9.009999999999999E-05</v>
       </c>
     </row>
     <row r="46">
@@ -1286,7 +1286,7 @@
         <v>1.205</v>
       </c>
       <c r="F46">
-        <v>0.000375375</v>
+        <v>0.000375</v>
       </c>
     </row>
     <row r="47">
@@ -1346,7 +1346,7 @@
         <v>20.56</v>
       </c>
       <c r="F49">
-        <v>0.00144866666666667</v>
+        <v>0.001448667</v>
       </c>
     </row>
     <row r="50">
@@ -1466,7 +1466,7 @@
         <v>2.425</v>
       </c>
       <c r="F55">
-        <v>0.00686957133333333</v>
+        <v>0.006869571</v>
       </c>
     </row>
     <row r="56">
@@ -1682,7 +1682,7 @@
         <v>1.5</v>
       </c>
       <c r="F66">
-        <v>0.00015625</v>
+        <v>0.000156</v>
       </c>
     </row>
     <row r="67">
@@ -1718,7 +1718,7 @@
         <v>1</v>
       </c>
       <c r="F68">
-        <v>0.000858666666666667</v>
+        <v>0.000859</v>
       </c>
     </row>
     <row r="69">
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="F70">
-        <v>9.315E-05</v>
+        <v>9.32E-05</v>
       </c>
     </row>
     <row r="71">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F71">
-        <v>0.0004115</v>
+        <v>0.000412</v>
       </c>
     </row>
     <row r="72">
@@ -1793,7 +1793,7 @@
         <v>0.61</v>
       </c>
       <c r="F72">
-        <v>0.0003934</v>
+        <v>0.000393</v>
       </c>
     </row>
     <row r="73">
@@ -1814,7 +1814,7 @@
         <v>1.1</v>
       </c>
       <c r="F73">
-        <v>0.0006935</v>
+        <v>0.000694</v>
       </c>
     </row>
     <row r="74">
@@ -1874,7 +1874,7 @@
         <v>0.91</v>
       </c>
       <c r="F76">
-        <v>0.000105722</v>
+        <v>0.000106</v>
       </c>
     </row>
     <row r="77">
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="F77">
-        <v>0.000127333</v>
+        <v>0.000127</v>
       </c>
     </row>
     <row r="78">
@@ -2039,7 +2039,7 @@
         <v>21</v>
       </c>
       <c r="F85">
-        <v>0.0066065835</v>
+        <v>0.006606584</v>
       </c>
     </row>
     <row r="86">
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="F87">
-        <v>0.000459667</v>
+        <v>0.00046</v>
       </c>
     </row>
     <row r="88">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F90">
-        <v>0.0016241665</v>
+        <v>0.001624167</v>
       </c>
     </row>
   </sheetData>
